--- a/MinMax/scripts/comparison/violations_comparison_table_118_10.xlsx
+++ b/MinMax/scripts/comparison/violations_comparison_table_118_10.xlsx
@@ -459,16 +459,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>0.001097457832656801</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.0004272309015505016</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>0.01282527111470699</v>
+        <v>0.012821807526052</v>
       </c>
       <c r="E2">
-        <v>0.01597344502806664</v>
+        <v>0.01596958562731743</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -476,10 +476,10 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>0.08803081512451172</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>0.04157733917236328</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>0.1537753939628601</v>
@@ -493,16 +493,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>0.0003323077980894595</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>0.000298106751870364</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>0.006021232344210148</v>
+        <v>0.006022310815751553</v>
       </c>
       <c r="E4">
-        <v>0.00529688224196434</v>
+        <v>0.005297569558024406</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -510,16 +510,16 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>0.04352374747395515</v>
+        <v>-0</v>
       </c>
       <c r="C5">
-        <v>0.069937564432621</v>
+        <v>-0</v>
       </c>
       <c r="D5">
         <v>0.09141665697097778</v>
       </c>
       <c r="E5">
-        <v>0.09197986125946045</v>
+        <v>0.09221160411834717</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -570,7 +570,7 @@
         <v>0.0006122473860159516</v>
       </c>
       <c r="E8">
-        <v>0.00260470830835402</v>
+        <v>0.002604708541184664</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -629,10 +629,10 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>0.0001609358296263963</v>
+        <v>0.0001609608734725043</v>
       </c>
       <c r="C12">
-        <v>0.00016095805040095</v>
+        <v>0.0001609651662874967</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -646,10 +646,10 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>0.01916271448135376</v>
+        <v>0.01916515827178955</v>
       </c>
       <c r="C13">
-        <v>0.01915949583053589</v>
+        <v>0.01916044950485229</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -663,10 +663,10 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>0.1711081117391586</v>
+        <v>0.1711168885231018</v>
       </c>
       <c r="C14">
-        <v>0.1711189299821854</v>
+        <v>0.1711201816797256</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -680,10 +680,10 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>8.22471809387207</v>
+        <v>8.22465705871582</v>
       </c>
       <c r="C15">
-        <v>8.225234985351562</v>
+        <v>8.224760055541992</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -697,16 +697,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>5.834673176770847E-08</v>
+        <v>5.944280571381453E-08</v>
       </c>
       <c r="C16">
-        <v>6.081153626597375E-08</v>
+        <v>6.129458339177998E-08</v>
       </c>
       <c r="D16">
-        <v>2.014752060509379E-06</v>
+        <v>2.020443844230613E-06</v>
       </c>
       <c r="E16">
-        <v>1.950270993533036E-06</v>
+        <v>1.928794745253981E-06</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -714,16 +714,16 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>2.023590276975042E-06</v>
+        <v>2.594122865991642E-06</v>
       </c>
       <c r="C17">
-        <v>2.935085482071499E-06</v>
+        <v>2.57349779447589E-06</v>
       </c>
       <c r="D17">
-        <v>4.387940487175952E-05</v>
+        <v>3.486841160338372E-05</v>
       </c>
       <c r="E17">
-        <v>3.578327571948287E-05</v>
+        <v>4.780068047693931E-05</v>
       </c>
     </row>
   </sheetData>
